--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D985E09-09F3-4E25-A735-6AD76EA0C6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7607AC29-B497-4BA0-9E65-E45226849B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="1065" windowWidth="25005" windowHeight="14355" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" tabRatio="804" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="240">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -10944,7 +10944,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11568,7 +11568,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" ref="A18:A37" si="2">ROW()-2+20000</f>
+        <f t="shared" ref="A18:A36" si="2">ROW()-2+20000</f>
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -12148,7 +12148,7 @@
         <v>20032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -12160,10 +12160,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="G34">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -12184,7 +12184,7 @@
         <v>20033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -12196,10 +12196,10 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="G35">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -12220,7 +12220,7 @@
         <v>20034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -12232,10 +12232,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G36">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -12247,42 +12247,6 @@
         <v>1010</v>
       </c>
       <c r="K36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <f t="shared" si="2"/>
-        <v>20035</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>3000</v>
-      </c>
-      <c r="G37">
-        <v>1500</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>1010</v>
-      </c>
-      <c r="K37">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb85b1299b9076c2/ドキュメント/Unity/Okashi_Atlier2/Assets/Resources/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7607AC29-B497-4BA0-9E65-E45226849B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{7607AC29-B497-4BA0-9E65-E45226849B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B2183CD-C355-43CF-8148-D5FADC6C18C6}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" tabRatio="804" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3270" yWindow="1650" windowWidth="23295" windowHeight="13305" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="241">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -995,6 +995,10 @@
   </si>
   <si>
     <t>red_jemstone</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>skillreset_ticket</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1066,6 +1070,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5147,7 +5155,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5230,7 +5238,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A85" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A86" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5462,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -5570,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -5642,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -5678,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -5714,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -6038,7 +6046,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G25">
         <v>3</v>
@@ -6110,10 +6118,10 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -6149,7 +6157,7 @@
         <v>5</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -6218,7 +6226,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -6290,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -6890,10 +6898,10 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D49">
         <v>6</v>
@@ -6902,10 +6910,10 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -6926,7 +6934,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6938,13 +6946,13 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6962,7 +6970,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6971,16 +6979,16 @@
         <v>6</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -6998,22 +7006,22 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>6</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -7034,7 +7042,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="C53">
         <v>10</v>
@@ -7043,7 +7051,7 @@
         <v>6</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>2</v>
@@ -7070,10 +7078,10 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D54">
         <v>6</v>
@@ -7082,13 +7090,13 @@
         <v>1</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -7106,7 +7114,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7115,13 +7123,13 @@
         <v>6</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -7142,7 +7150,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7178,7 +7186,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7214,7 +7222,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7250,7 +7258,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7286,7 +7294,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7322,7 +7330,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7358,7 +7366,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7394,7 +7402,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7430,7 +7438,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7466,7 +7474,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7502,7 +7510,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7538,7 +7546,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7574,7 +7582,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>233</v>
+        <v>137</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7583,16 +7591,16 @@
         <v>6</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -7610,7 +7618,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7619,16 +7627,16 @@
         <v>6</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -7646,7 +7654,7 @@
         <v>2068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7655,13 +7663,13 @@
         <v>6</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H70">
         <v>2000</v>
@@ -7682,7 +7690,7 @@
         <v>2069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7694,7 +7702,7 @@
         <v>1</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G71">
         <v>2</v>
@@ -7718,7 +7726,7 @@
         <v>2070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7730,10 +7738,10 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H72">
         <v>2000</v>
@@ -7754,7 +7762,7 @@
         <v>2071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7766,13 +7774,13 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -7790,7 +7798,7 @@
         <v>2072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7802,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -7826,7 +7834,7 @@
         <v>2073</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7844,7 +7852,7 @@
         <v>2</v>
       </c>
       <c r="H75">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -7862,7 +7870,7 @@
         <v>2074</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7874,10 +7882,10 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H76">
         <v>2000</v>
@@ -7898,7 +7906,7 @@
         <v>2075</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7907,16 +7915,16 @@
         <v>6</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="G77">
         <v>5</v>
       </c>
-      <c r="G77">
-        <v>2</v>
-      </c>
       <c r="H77">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
@@ -7934,7 +7942,7 @@
         <v>2076</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7970,7 +7978,7 @@
         <v>2077</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7982,13 +7990,13 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I79" t="b">
         <v>0</v>
@@ -8006,7 +8014,7 @@
         <v>2078</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -8018,10 +8026,10 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>2000</v>
@@ -8042,7 +8050,7 @@
         <v>2079</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -8054,10 +8062,10 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81">
         <v>2000</v>
@@ -8078,7 +8086,7 @@
         <v>2080</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -8114,7 +8122,7 @@
         <v>2081</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>228</v>
+        <v>148</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -8126,10 +8134,10 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H83">
         <v>2000</v>
@@ -8150,7 +8158,7 @@
         <v>2082</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -8162,10 +8170,10 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84">
         <v>2000</v>
@@ -8186,7 +8194,7 @@
         <v>2083</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -8198,10 +8206,10 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>2000</v>
@@ -8213,6 +8221,42 @@
         <v>100</v>
       </c>
       <c r="K85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <f t="shared" si="0"/>
+        <v>2084</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>6</v>
+      </c>
+      <c r="G86">
+        <v>2</v>
+      </c>
+      <c r="H86">
+        <v>2000</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>100</v>
+      </c>
+      <c r="K86">
         <v>1</v>
       </c>
     </row>
@@ -10053,10 +10097,10 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="G51">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -11584,10 +11628,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G18">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -12602,7 +12646,7 @@
         <v>82</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -12638,7 +12682,7 @@
         <v>83</v>
       </c>
       <c r="C11">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -13223,10 +13267,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G27">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H27">
         <v>1</v>
